--- a/Result/profitability/3092.xlsx
+++ b/Result/profitability/3092.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -668,7 +668,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>8.385</v>
+        <v>8.053750000000001</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -777,7 +777,7 @@
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>8.623750000000001</v>
+        <v>8.01375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -789,7 +789,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -890,7 +890,7 @@
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>7.83</v>
+        <v>8.28125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>7.52125</v>
+        <v>7.945</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>8.315</v>
+        <v>9.6625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>10.3075</v>
+        <v>11.4875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>11.795</v>
+        <v>12.00875</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9800,6 +9800,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3092</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>417</v>
+      </c>
+      <c r="D75" t="n">
+        <v>371</v>
+      </c>
+      <c r="E75" t="n">
+        <v>46</v>
+      </c>
+      <c r="F75" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-113</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-27.01%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-115</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-132</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-1.11875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>8.275</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3052631578947369</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.709999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1850649350649349</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.7699999999999998</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.3830845771144278</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.4484126984126984</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
